--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -826,7 +826,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
@@ -840,7 +844,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính phần fan-out và phần bộ tổng hợp riêng rồi cộng.</t>
+          <t>Số lượt chạy nhánh ban đầu = 75 hồ sơ × 4 nhánh = 300 lượt. Số nhánh bị hết thời gian chờ và được thử lại đúng một lần là 5% của 300 = 15 lượt. Tổng số lượt chạy nhánh gồm cả lượt thử lại là 300 + 15 = 315 lượt.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -627,10 +627,22 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách quyền dữ liệu, độ bao phủ đánh giá và người chịu trách nhiệm vận hành.
-Phân tích theo nguyên lý thiết kế: Tách quyền dữ liệu, độ bao phủ đánh giá và người chịu trách nhiệm vận hành.</t>
+- Đánh dấu chuẩn xác Đã có / Còn thiếu / Mâu thuẫn (1.5 điểm): Xác định đúng phần đã có (quy trình, data consent, rollback), còn thiếu (lỗi hiếm, người nhận alert) và mâu thuẫn (baseline thiên kiến ca thuận lợi).
+- Gán bước kiểm chứng và người phụ trách cho từng khoảng trống (1.5 điểm): Nêu rõ đo lại baseline (PM), thêm lỗi hiếm vào eval (QA), gán trực on-call nhận alert (SRE).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Rà soát sổ kiểm tra độ sẵn sàng AI (AI Readiness Checklist):
+1. Đánh giá trạng thái ĐÃ CÓ / CÒN THIẾU / MÂU THUẪN:
+- ĐÃ CÓ: (1) Quy trình nghiệp vụ và người phụ trách đã xác nhận rõ ràng; (2) 1.200 nhật ký có sự đồng ý sử dụng dữ liệu rõ ràng; (3) Có cơ chế đường lui (rollback) khi sự cố.
+- CÒN THIẾU: (1) Bộ đánh giá chưa bao phủ các trường hợp lỗi hiếm (Missing Edge/Rare Cases); (2) Chưa có nhân sự phụ trách tiếp nhận và xử lý cảnh báo vận hành (Missing Alert Ownership).
+- MÂU THUẪN / THIÊN KIẾN: Đường cơ sở thủ công chỉ đo lường các ca thuận lợi (Baseline Selection Bias), tạo ra mốc so sánh giả tạo không phản ánh đúng thực tế phức tạp của quy trình.
+2. Gán bước kiểm chứng tiếp theo và người phụ trách cho từng khoảng trống:
+- Xử lý mốc nền thiên kiến: Đo bổ sung tối thiểu 50 trường hợp thủ công phức tạp/ngoại lệ để thiết lập mốc nền trung thực. Người phụ trách: Quản lý Sản phẩm (Product Manager).
+- Xử lý bộ đánh giá thiếu lỗi hiếm: Biên soạn bộ dữ liệu kiểm thử đối kháng gồm 50 ca biên lỗi hiếm và dị thường. Người phụ trách: Kỹ sư Đảm bảo Chất lượng AI (AI QA Engineer).
+- Xử lý thiếu người nhận cảnh báo: Thiết lập lịch trực on-call và tích hợp PagerDuty. Người phụ trách: Trưởng nhóm Vận hành SRE (SRE Lead).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Ma trận sẵn sàng AI (AI Readiness Scorecard) phân biệt giữa 'Sẵn sàng bề mặt' và 'Sẵn sàng sản xuất thực thụ'. Đường cơ sở chỉ đo ca thuận lợi là một hình thức gian lận số liệu vô thức (Self-deception) khiến hệ thống ngã gục khi vừa gặp lưu lượng thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI Risk Management Framework (NIST AI 100-1) (https://www.nist.gov/itl/ai-risk-management-framework); Google Cloud MLOps Assessment.</t>
         </is>
       </c>
     </row>
@@ -663,10 +675,23 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đánh dấu yêu cầu nào cho phép bất định và yêu cầu nào tuyệt đối không được sai.
-Phân tích theo nguyên lý thiết kế: Đánh dấu yêu cầu nào cho phép bất định và yêu cầu nào tuyệt đối không được sai.</t>
+- Phân bổ chính xác phần xác suất và xác định (1.0 điểm): Giao LLM đọc mô tả kinh nghiệm; giao code tất định kiểm tra tuổi, giới tính và giấy phép.
+- Thiết kế đủ 3 điểm kiểm soát bất biến (2.0 điểm): Nêu rõ kiểm tra tuổi &gt;=18, lọc bỏ giới tính chống thiên kiến, và chuyển người duyệt khi thiếu giấy phép.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân bổ phần xác suất và phần xác định trong quy trình tuyển dụng:
+- Phần xác suất (Probabilistic Task -&gt; Giao cho LLM): Đọc hiểu văn bản mô tả kinh nghiệm làm việc tự do của ứng viên, trích xuất danh sách các kỹ năng kỹ thuật, vị trí đã từng làm và số năm kinh nghiệm thành JSON có cấu trúc.
+- Phần xác định (Deterministic Invariants -&gt; Giao cho Mã nguồn tất định): Kiểm tra toàn bộ các điều kiện pháp lý và chính sách bất biến bằng code Python/SQL, tuyệt đối không dùng LLM để phán xét.
+2. Thiết kế các bước kiểm tra và điểm kiểm soát bất biến (Control Gates):
+- Cổng kiểm soát 1 (Ràng buộc tuổi lao động bắt buộc):
+  `assert applicant_age &gt;= 18, 'Candidate is under legal working age'` -&gt; Nếu dưới 18 tuổi, hệ thống tự động từ chối ngay lập tức do vi phạm quy định pháp luật lao động.
+- Cổng kiểm soát 2 (Chống phân biệt đối xử theo giới tính):
+  Loại bỏ hoàn toàn trường giới tính (Gender stripping) ra khỏi prompt trước khi gửi vào LLM; đồng thời mã nguồn chạy kiểm tra độc lập đảm bảo tỷ lệ qua vòng lọc sơ bộ không có sự sai lệch có ý nghĩa thống kê giữa các nhóm giới tính (Fairness Disparate Impact Check).
+- Cổng kiểm soát 3 (Xử lý thiếu giấy phép bắt buộc):
+  Code kiểm tra danh mục giấy phép hành nghề: `if not has_required_license: route_to_human_reviewer()` -&gt; Lập tức chuyển hồ sơ sang hàng đợi của Chuyên viên tuyển dụng con người để liên hệ xác minh, tuyệt đối không để LLM tự ý từ chối hồ sơ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tuân thủ Đạo luật AI của EU và Luật Lao động về hệ thống AI tuyển dụng rủi ro cao: Ràng buộc độ tuổi và chống phân biệt đối xử là các bất biến pháp lý không thể thương lượng. Tách biệt hoàn toàn trường giới tính và dùng mã nguồn tất định kiểm soát ranh giới bảo vệ tổ chức khỏi các vụ kiện tụng phân biệt đối xử.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Equal Employment Opportunity Commission (EEOC) - Guidance on AI and Title VII; Barocas, S., et al. (2019). Fairness and Machine Learning (https://fairmlbook.org/)</t>
         </is>
       </c>
     </row>
@@ -803,10 +828,25 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đánh dấu đầu vào nào phải tồn tại trước khi từng nhánh được chạy.
-Phân tích theo nguyên lý thiết kế: Đánh dấu đầu vào nào phải tồn tại trước khi từng nhánh được chạy.</t>
+- Vẽ rõ quan hệ phụ thuộc và phân nhánh song song (1.0 điểm): Nhánh bảo mật và pháp lý chạy ngay trên code snapshot; nhánh build kích hoạt nhánh kiểm thử hiệu năng.
+- Thiết kế điểm đồng bộ và tổng hợp kết quả (1.0 điểm): Điểm rào cản (Join barrier) đợi cả 3 nhánh và tổng hợp thành bản ghi chú phát hành thống nhất.
+- Cơ chế xử lý lỗi từng phần (1.0 điểm): Bảo toàn kết quả các nhánh thành công, cho phép retry độc lập nhánh lỗi mà không cần chạy lại toàn bộ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế mô hình song song hóa (Parallelization Pattern) cho quy trình rà soát bản phát hành:
+1. Quan hệ phụ thuộc và phân nhánh song song (Fan-Out Structure):
+- Tiền điều kiện: Ảnh chụp mã nguồn (Source Code Snapshot) được đóng băng (Tagged / Frozen Commit) tại kho Git.
+- Nhánh độc lập 1: [Rà soát bảo mật mã nguồn (SAST/Security Scan)] -&gt; Chạy trực tiếp trên Source Snapshot.
+- Nhánh độc lập 2: [Rà soát pháp lý bản quyền (License Compliance Scan)] -&gt; Quét bảng kê giấy phép (SBOM) trích xuất từ Source Snapshot.
+- Nhánh tuần tự rồi song song: [Sản phẩm Build] được biên dịch từ Source Snapshot -&gt; Sau khi Build hoàn tất, lập tức kích hoạt Nhánh 3: [Kiểm thử hiệu năng tự động (Performance/Load Test)].
+2. Điểm đồng bộ hóa và cách tổng hợp (Fan-In Synchronization &amp; Aggregation):
+- Điểm đồng bộ hóa (Barrier Node / Join): Hệ thống chờ cả 3 nhánh (Bảo mật, Pháp lý, Hiệu năng) hoàn tất kết quả.
+- Tổng hợp: Bộ tổng hợp gom kết quả của 3 báo cáo có cấu trúc thành một bản 'Ghi chú phát hành hoàn chỉnh' (Release Gate Report) tóm tắt: Trạng thái lỗ hổng bảo mật, Tuân thủ giấy phép và Chỉ số P95 Latency/Throughput.
+3. Cách xử lý lỗi từng phần (Partial Failure Handling):
+- Nếu 1 nhánh bị lỗi hạ tầng (ví dụ máy chủ kiểm thử hiệu năng bị timeout): Hệ thống KHÔNG hủy bỏ kết quả của nhánh Bảo mật và Pháp lý; đánh dấu nhánh Hiệu năng là 'Thất bại do hạ tầng', giữ nguyên kết quả hai nhánh kia và cho phép chạy lại (Retry) duy nhất nhánh Hiệu năng để tiết kiệm thời gian.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mẫu hình Song song hóa (Fan-Out / Fan-In Parallelization Pattern) trong CI/CD và Multi-Agent Orchestration. Bằng cách phân tách các tác vụ độc lập để chạy đồng thời sau mốc đóng băng mã nguồn, thời gian rà soát phát hành giảm từ 3 tiếng xuống dưới 45 phút, đồng thời cơ chế Partial Retry giúp tối ưu hóa tài nguyên tính toán.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents: Parallelization Workflow (https://www.anthropic.com/research/building-effective-agents); Humble, J., &amp; Farley, D. (2010). Continuous Delivery.</t>
         </is>
       </c>
     </row>
@@ -877,10 +917,27 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách lỗi có thể viết lại khỏi lỗi cần người xác minh nguồn.
-Phân tích theo nguyên lý thiết kế: Tách lỗi có thể viết lại khỏi lỗi cần người xác minh nguồn.</t>
+- Tiêu chí kiểm định đủ 3 yếu tố y khoa (1.0 điểm): Trích dẫn chuẩn, không thêm chẩn đoán và giới hạn &lt;= 120 từ.
+- Phân loại lỗi viết lại vs lỗi nguồn (1.0 điểm): Cho phép sửa lỗi độ dài, chặn tự sửa lỗi trích dẫn/chẩn đoán.
+- Điều kiện dừng và chuyển bác sĩ (1.0 điểm): Dừng khi pass 3 tiêu chí hoặc chạm trần 3 vòng hoặc gặp lỗi nguồn để chuyển bác sĩ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế vòng lặp Generator–Evaluator cho tóm tắt y khoa:
+1. Bộ tiêu chí kiểm định nghiêm ngặt của Evaluator:
+- Tiêu chí 1 (Có trích dẫn hợp lệ - Grounded Citation): 100% dữ kiện lâm sàng phải có mã trích dẫn tương ứng với hồ sơ bệnh án gốc.
+- Tiêu chí 2 (Không thêm chẩn đoán mới - No Extrapolated Diagnosis): Tuyệt đối không tự suy diễn hoặc bổ sung các bệnh danh/chẩn đoán không có trong tài liệu gốc.
+- Tiêu chí 3 (Độ dài tối đa - Length Constraint): Toàn bộ bản tóm tắt phải &lt;= 120 từ.
+2. Cơ chế phản hồi có cấu trúc và phân loại lỗi:
+- Lỗi có thể viết lại (Rewritable Error - độ dài &gt; 120 từ hoặc văn phong rườm rà): Evaluator gửi phản hồi chỉ thị rõ: 'Cắt giảm 15 từ, giữ nguyên trích dẫn'. Generator tiếp tục tối ưu hóa.
+- Lỗi nghiêm trọng (Critical Source Error - trích dẫn sai hoặc bịa chẩn đoán): Lập tức dừng vòng lặp, KHÔNG cho Generator tự đoán mò để sửa.
+3. Điều kiện chấp nhận, dừng và chuyển người (Escalation):
+- Chấp nhận: Khi thỏa mãn cả 3 tiêu chí (&lt;= 120 từ, trích dẫn chuẩn 100%, không chẩn đoán thừa).
+- Dừng và chuyển bác sĩ (Human Escalation):
+  + Trường hợp 1: Phát hiện lỗi trích dẫn không tìm thấy trong nguồn hoặc vi phạm chẩn đoán mới.
+  + Trường hợp 2: Sau 3 vòng lặp (Max 3 iterations) vẫn vượt quá 120 từ. Toàn bộ bản thảo kèm báo cáo vi phạm được chuyển tiếp ngay cho Bác sĩ điều trị xem xét và hoàn thiện thủ công.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong lĩnh vực y tế (Healthcare AI), an toàn bệnh nhân là tối thượng. Phân biệt giữa 'Lỗi hình thức có thể tự sửa' (Format/Length) và 'Lỗi bản chất nguồn' (Factuality/Diagnosis). Khi AI bị ảo giác về nguồn dữ liệu y khoa, việc để AI tự sửa nguồn chỉ làm ảo giác sâu hơn; giải pháp an toàn duy nhất là chuyển ngay cho bác sĩ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents (Evaluator-Optimizer Workflow) (https://www.anthropic.com/research/building-effective-agents); AMA Guidelines for Augmented Intelligence in Healthcare.</t>
         </is>
       </c>
     </row>
@@ -913,10 +970,26 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách trường hợp thông thường khỏi ngoại lệ trước khi chọn mức tự chủ.
-Phân tích theo nguyên lý thiết kế: Tách trường hợp thông thường khỏi ngoại lệ trước khi chọn mức tự chủ.</t>
+- Chọn đúng bước tăng tự chủ và phân định phạm vi (1.0 điểm): Chuyển lên mức Human-on-the-loop (tự động hóa ca thông thường đã kiểm chứng 600 ca, người duyệt ca ngoại lệ mới 12 ca).
+- Điều kiện quay lui an toàn rõ ràng (1.0 điểm): Đặt ngưỡng rollback khi có 1 khiếu nại nghiêm trọng hoặc tỷ lệ can thiệp sửa đổi &gt; 5%.
+- Bằng chứng cần bổ sung định lượng (1.0 điểm): Yêu cầu tích lũy thêm 50-100 ca ngoại lệ trước khi mở rộng tiếp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Kế hoạch nâng cấp mức độ tự chủ có kiểm soát (Phased Autonomy Escalation):
+1. Chọn bước tăng mức tự chủ tiếp theo:
+Chuyển từ Cấp độ 2 (Hỗ trợ con người / Human-in-the-loop: AI gợi ý, người duyệt 100%) lên Cấp độ 3 (Tự động hóa có ngoại lệ / Human-on-the-loop: Tự động thực thi đối với các ca thông thường, con người chỉ duyệt các ca ngoại lệ/nguy cơ).
+2. Phạm vi áp dụng chặt chẽ (Scope Boundary):
+- Phạm vi ĐƯỢC TỰ ĐỘNG THỰC THI: Chỉ áp dụng cho các yêu cầu đổi lịch giao hàng thông thường (Standard Requests) thỏa mãn đồng thời: khách dời lịch trong vòng 24–48 giờ, địa chỉ không đổi, đơn hàng chưa xuất kho và thuộc nhóm 600 trường hợp đã được kiểm chứng an toàn.
+- Phạm vi BẮT BUỘC CHUYỂN NGƯỜI DUYỆT (Escalate): 100% các yêu cầu thuộc chính sách ngoại lệ mới (12 trường hợp) hoặc đơn hàng có giá trị cao, đổi địa chỉ nhận hàng, hoặc dời lịch quá 3 ngày.
+3. Điều kiện quay lui khẩn cấp (Rollback Trigger Conditions):
+- Kích hoạt nút dừng (Emergency Kill Switch) và hạ cấp ngay về Cấp độ 2 (người duyệt 100%) nếu:
+  + Xuất hiện bất kỳ 1 khiếu nại nghiêm trọng nào từ khách hàng về việc giao sai lịch tự động.
+  + Hoặc tỷ lệ người vận hành phải can thiệp sửa đổi đơn sau khi hệ thống tự xếp lịch vượt quá 5% trong tuần.
+4. Bằng chứng cần bổ sung trước khi mở rộng hoàn toàn:
+Cần thu thập và thử nghiệm đối chứng tối thiểu thêm 50–100 trường hợp thực tế thuộc chính sách ngoại lệ mới để đo lường độ chính xác trước khi xem xét cấp quyền tự động cho nhóm này.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Khung leo thang tự chủ theo giai đoạn (Phased Autonomy Framework / SAE Levels of Automation): Tuyệt đối không nhảy cóc từ 'Gợi ý' sang 'Tự động hoàn toàn 100%'. Phân tách các luồng nghiệp vụ thành vùng an toàn (Standard) và vùng chưa kiểm chứng (Exceptions), kết hợp điều kiện ngắt mạch tự động (Circuit Breaker) bảo đảm quá trình chuyển giao mượt mà và an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Parasuraman, R., et al. (2000). A Model for Types and Levels of Human Interaction with Automation (https://ieeexplore.ieee.org/document/844357); Google PAIR Guidebook - Phased Autonomy.</t>
         </is>
       </c>
     </row>
@@ -950,10 +1023,20 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu từng nguồn, ngày và phần còn thiếu trước khi kết luận.
-Phân tích theo nguyên lý thiết kế: Nêu từng nguồn, ngày và phần còn thiếu trước khi kết luận.</t>
+- Minh bạch nguồn và độ mới của từng tài liệu (1.0 điểm): Nêu rõ nguồn A (30 ngày, 10 ngày trước) và nguồn B (60 ngày, không ngày cập nhật).
+- Nêu rõ điểm bất định về khu vực áp dụng (1.0 điểm): Chỉ ra độ không chắc chắn về khu vực của người dùng.
+- Giới hạn hành động và hướng dẫn an toàn (1.0 điểm): Khóa xác nhận hoàn tiền ngoài 30 ngày, hướng dẫn liên hệ CSKH xác minh.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Viết lại câu trả lời với mức độ minh bạch bằng chứng chuẩn xác:
+\"Hiện có sự mâu thuẫn giữa các tài liệu chính sách về thời hạn hoàn tiền:
+- Theo Nguồn A (vừa cập nhật 10 ngày trước): Thời hạn cho phép hoàn tiền là trong vòng 30 ngày.
+- Theo Nguồn B (tài liệu không ghi rõ ngày cập nhật): Ghi nhận thời hạn là 60 ngày.
+- Độ không chắc chắn: Hệ thống chưa có dữ liệu xác định chính sách nào có hiệu lực cho khu vực địa lý của bạn.
+Giới hạn hành động: Để đảm bảo quyền lợi và tránh hiểu lầm, hệ thống tạm thời chưa thể xác nhận yêu cầu hoàn tiền cho trường hợp ngoài 30 ngày. Khuyến nghị: Bạn vui lòng cung cấp thông tin khu vực/chi nhánh mua hàng hoặc liên hệ trực tiếp bộ phận Chăm sóc khách hàng để được xác nhận chính sách áp dụng chính thức.\"
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Minh bạch Nguồn và Quản trị Độ không chắc chắn (Epistemic Transparency): Khi gặp các nguồn dữ liệu xung đột nhau về thời gian và phạm vi hiệu lực, hệ thống AI có đạo đức không được quyền tự ý chọn nguồn thuận lợi. Bộc lộ mâu thuẫn, công khai độ mới của nguồn và khóa hành động rủi ro là biện pháp bảo vệ khách hàng tốt nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Explain System Limitations and Confidence (https://pair.withgoogle.com/guidebook/); ISO/IEC 42001 - Artificial Intelligence Management System.</t>
         </is>
       </c>
     </row>
@@ -985,10 +1068,24 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Liệt kê điều người duyệt cần biết để chịu trách nhiệm cho hành động có hậu quả.
-Phân tích theo nguyên lý thiết kế: Liệt kê điều người duyệt cần biết để chịu trách nhiệm cho hành động có hậu quả.</t>
+- Thiết kế dữ liệu phê duyệt đầy đủ thông tin rủi ro (1.0 điểm): Hiển thị số tiền 85tr (vượt trần 50tr), trích dẫn hóa đơn và cảnh báo điểm gian lận 0,58.
+- Hành vi chi tiết khi Chấp thuận, Chỉnh sửa, Từ chối (1.5 điểm): Nêu rõ chữ ký số/OTP khi duyệt, cho phép sửa số tiền và quy trình từ chối ghi log rủi ro.
+- Đặt điểm phê duyệt chốt chặn trước khi gọi API giải ngân (0.5 điểm): Khẳng định giao dịch bị khóa tại cổng cho đến khi có chữ ký cấp quản lý.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế dữ liệu phê duyệt trên màn hình người duyệt (Approval Data Payload):
+- Thông tin số tiền và cảnh báo vượt hạn mức: 'SỐ TIỀN YÊU CẦU HOÀN: 85.000.000 VNĐ' (Cảnh báo đỏ: Vượt hạn mức tự duyệt 50 triệu đồng theo Chính sách tài chính Điều 3).
+- Bằng chứng trích dẫn: Trích dẫn hóa đơn gốc, mã giao dịch, lịch sử mua hàng và văn bản khiếu nại của khách hàng.
+- Chỉ số rủi ro: Cảnh báo điểm tin cậy gian lận thấp: 'Fraud Confidence Score = 0,58 (Mức độ nghi vấn trung bình - Cần thẩm định kỹ)'.
+- Thẩm quyền phê duyệt: Chỉ hiển thị nút duyệt cho tài khoản có vai trò 'Giám đốc Chi nhánh / Quản lý Tài chính cấp cao'.
+2. Thiết kế hành vi chi tiết theo từng quyết định của người duyệt:
+- Khi CHẤP THUẬN (Approve): Bắt buộc người duyệt nhập lý do phê duyệt ngoại lệ và xác thực mã OTP/Chữ ký số. Hệ thống gọi API hoàn tiền Core Banking và ghi nhận Audit Log bất biến.
+- Khi CHỈNH SỬA (Modify): Cho phép người duyệt điều chỉnh lại số tiền hoàn (ví dụ giảm xuống 50 triệu theo hạn mức bảo hiểm), đính kèm giải thích cho khách hàng và gửi yêu cầu xác nhận lại.
+- Khi TỪ CHỐI (Reject): Người duyệt chọn lý do từ chối (nghi ngờ gian lận/hóa đơn không hợp lệ). Hệ thống đóng yêu cầu, gửi email giải thích chuẩn mực cho khách hàng và gắn cờ tài khoản vào danh sách theo dõi rủi ro.
+3. Điểm chốt chặn: Toàn bộ lệnh hoàn tiền bị phong tỏa tại cổng thanh toán cho đến khi nhận được token phê duyệt có chữ ký điện tử hợp lệ của cấp quản lý.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Chốt chặn Tài chính (Financial Authorization Boundary): Một khoản tiền lớn (85 triệu) vượt hạn mức 50 triệu và có chỉ số nghi vấn gian lận (0,58) tuyệt đối không được phép tự động giải ngân. Màn hình phê duyệt phải cung cấp đầy đủ bối cảnh rủi ro để người duyệt chịu trách nhiệm giải trình cá nhân.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST SP 800-53 Rev. 5 - Access Control &amp; Separation of Duties (https://csrc.nist.gov/publications/detail/sp/800-53/rev-5/final); Microsoft HAX Toolkit - Guideline 11: Make Clear Why the System Did What It Did (https://www.microsoft.com/en-us/haxtoolkit/).</t>
         </is>
       </c>
     </row>
@@ -1019,10 +1116,24 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nói rõ phần nào thành công, phần nào chưa và hành động nào bị khóa.
-Phân tích theo nguyên lý thiết kế: Nói rõ phần nào thành công, phần nào chưa và hành động nào bị khóa.</t>
+- Trạng thái hiển thị trung thực, không giả tạo xác minh (1.0 điểm): Nêu rõ bản nháp đã tạo nhưng chưa xác minh trích dẫn do timeout, gắn nhãn Unverified.
+- Bảo toàn an toàn dữ liệu đã tạo (1.0 điểm): Lưu trữ nguyên vẹn bản nháp và dữ liệu người dùng để người dùng yên tâm rời phiên.
+- Phương án phục hồi và khóa hành động xuất bản (1.0 điểm): Khóa nút gửi/publish đối ngoại, cung cấp cơ chế tự động verify lại ngầm và thông báo sau.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Trạng thái hiển thị minh bạch cho người dùng (UI Status Display):
+- Thông báo rõ ràng: 'Bản nháp báo cáo đã được tạo thành công từ dữ liệu của bạn. Tuy nhiên, Dịch vụ kiểm tra nguồn trích dẫn đang bị gián đoạn (Timeout) nên các số liệu và trích dẫn trong báo cáo CHƯA ĐƯỢC XÁC MINH NGUỒN GỐC.'
+- Gắn nhãn trạng thái trực quan: 'BẢN NHÁP CHƯA XÁC MINH' (Unverified Draft - Cảnh báo màu vàng) trên toàn bộ tiêu đề và từng trang tài liệu.
+2. Phần dữ liệu được bảo toàn an toàn (Preserved Data):
+- Hệ thống lưu trữ an toàn 100% nội dung bản nháp báo cáo đã sinh và dữ liệu thô người dùng đã tải lên vào cơ sở dữ liệu kèm mã `DraftID`. Người dùng hoàn toàn có thể an tâm rời phiên làm việc mà không bị mất dữ liệu đã xử lý.
+3. Các phương án phục hồi và Hành động bị khóa (Recovery Options &amp; Locked Actions):
+- Hành động BỊ KHÓA: Nút 'Xuất bản chính thức' (Publish) và 'Gửi báo cáo qua email cho ban lãnh đạo' bị tạm khóa cứng để ngăn chặn việc phát tán thông tin chưa kiểm chứng.
+- Các phương án phục hồi khi người dùng quay lại:
+  + Phương án 1 (Tự động chạy ngầm): Hệ thống tự động lên lịch chạy lại tác vụ kiểm tra trích dẫn trong nền khi dịch vụ phục hồi và gửi email thông báo khi báo cáo đã xác minh xong.
+  + Phương án 2 (Thủ công): Người dùng có thể bấm nút 'Thử xác minh lại nguồn ngay' hoặc tự tải bản nháp về máy cá nhân dưới dạng 'Bản thảo nội bộ'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Suy giảm Duyên dáng và Tính trung thực (Graceful Degradation &amp; Honesty): Tuyệt đối không giả vờ hệ thống đã hoàn thành 100% khi một thành phần kiểm định quan trọng bị lỗi. Bảo tồn công sức của người dùng (giữ nguyên bản nháp), gắn nhãn ranh giới chưa xác minh và khóa các hành động có hậu quả cao giúp cân bằng hoàn hảo giữa tính hữu ích và tính an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nielsen Norman Group - Graceful Degradation in UX; Google PAIR Guidebook - Errors &amp; Graceful Failure (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1056,10 +1167,25 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So từng thuộc tính của đầu vào mới với phạm vi đã kiểm thử.
-Phân tích theo nguyên lý thiết kế: So từng thuộc tính của đầu vào mới với phạm vi đã kiểm thử.</t>
+- Mệnh đề ODD chuẩn mực 3 điều kiện (1.0 điểm): Định nghĩa rõ giới hạn ngôn ngữ (Việt/Anh), độ dài (&lt;=5 trang, nét/thẳng) và 3 mẫu nhà cung cấp.
+- Bộ phát hiện OOD cụ thể (1.0 điểm): Nhận diện đúng tiếng Nhật, số trang 12 &gt; 5 và góc nghiêng ảnh qua thuật toán.
+- Hành vi suy giảm an toàn (1.0 điểm): Dừng tự động, thông báo lý do rõ ràng và chuyển giao cho đội nhập liệu con người.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Mệnh đề miền thiết kế vận hành (Operational Design Domain - ODD Statement):
+Hệ thống OCR hóa đơn chỉ được bảo đảm độ chính xác theo cam kết SLA KHI VÀ CHỈ KHI thỏa mãn đồng thời 3 điều kiện:
+- Ngôn ngữ tài liệu: Chỉ hỗ trợ tiếng Việt và tiếng Anh.
+- Chất lượng và độ dài tài liệu: Tệp ảnh/PDF có độ phân giải rõ nét (&gt; 200 DPI), hướng chụp thẳng (độ nghiêng góc skew &lt; 5 độ), độ dài tối đa không quá 5 trang.
+- Mẫu hóa đơn: Thuộc 3 mẫu nhà cung cấp đã được định nghĩa và kiểm thử chuẩn hóa.
+2. Bộ phát hiện đầu vào ngoài phạm vi (Out-of-ODD Detector):
+- Bộ phát hiện ngôn ngữ: Thư viện nhận diện ngôn ngữ (fastText/LangDetect) phát hiện tiếng Nhật (ký tự Hiragana/Katakana/Kanji) ngay ở trang đầu.
+- Bộ kiểm tra cấu trúc tệp: Đếm số trang vượt ngưỡng quy định ($12 &gt; 5$ trang).
+- Bộ kiểm tra chất lượng hình học ảnh: Thuật toán Hough Transform phát hiện góc xoay nghiêng quá mức (Skew angle &gt; 15 độ).
+3. Hành vi suy giảm có kiểm soát cho đầu vào mới (Graceful Degradation):
+Hệ thống KHÔNG CỐ GẮNG OCR TỰ ĐỘNG để tránh sinh rác dữ liệu: (1) Lập tức dừng xử lý tự động; (2) Hiển thị thông báo giải thích cụ thể: 'Tệp hóa đơn vi phạm ODD: Ngôn ngữ tiếng Nhật chưa được hỗ trợ, vượt quá 5 trang (12 trang) và ảnh bị nghiêng'; (3) Định tuyến tự động toàn bộ tệp hóa đơn sang hàng đợi xử lý chuyên biệt của đội ngũ nhập liệu thủ công kèm gắn nhãn cảnh báo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tiêu chuẩn kỹ nghệ ODD áp dụng cho hệ thống thị giác máy tính và trích xuất tài liệu. Đầu vào tiếng Nhật, 12 trang, ảnh nghiêng vi phạm cả 3 trụ cột của ODD. Từ chối xử lý tự động và chuyển luồng con người (Hand-off) bảo vệ cơ sở dữ liệu doanh nghiệp khỏi ô nhiễm dữ liệu rác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SAE J3016 Standard - Operational Design Domain; Google Cloud Document AI Best Practices (https://cloud.google.com/document-ai/docs/best-practices)</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1220,22 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết hai mẫu số riêng rồi hỏi loại lỗi nào gây hậu quả nặng hơn.
-Phân tích theo nguyên lý thiết kế: Viết hai mẫu số riêng rồi hỏi loại lỗi nào gây hậu quả nặng hơn.</t>
+- Tính chính xác Precision và Recall (1.5 điểm): Tính đúng Precision = 90.0% (54/60) và Recall = 60.0% (54/90).
+- Đề xuất hướng vận hành có điều kiện chuẩn xác (1.5 điểm): Ưu tiên tối đa hóa Precision để tránh khóa nhầm, sử dụng Step-up Auth (OTP/sinh trắc) cho vùng đệm trung bình thay vì khóa thẳng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Precision và Recall từ ma trận nhầm lẫn ($TP=54, FP=6, FN=36$):
+- Độ chính xác (Precision): $	ext{Precision} = \frac{TP}{TP + FP} = \frac{54}{54 + 6} = \frac{54}{60} = 0.900$ (90,0%).
+- Độ bao phủ (Recall): $	ext{Recall} = \frac{TP}{TP + FN} = \frac{54}{54 + 36} = \frac{54}{90} = 0.600$ (60,0%).
+2. Đề xuất hướng vận hành có điều kiện (Conditional Operational Strategy):
+- Phân tích hậu quả vận hành: Lỗi False Positive (FP) có hậu quả tức thì và nghiêm trọng (khóa nhầm tài khoản/giao dịch của khách hàng hợp lệ, gây khiếu nại gay gắt và tốn nguồn lực rà soát khẩn cấp). Trong khi đó, False Negative (FN) chỉ đưa giao dịch sang kiểm tra chậm hơn ở tuyến sau mà không gây gián đoạn trực tiếp cho khách hàng.
+- Hướng vận hành có điều kiện:
+  + Chiến lược: Duy trì và nâng cao hơn nữa PRECISION (mục tiêu &gt; 95%) để triệt tiêu lỗi khóa nhầm khách hàng tốt (giảm FP về sát 0).
+  + Điều kiện kích hoạt khóa tự động: Chỉ tự động khóa giao dịch khi mô hình đạt điểm tự tin cực cao (High Confidence Threshold &gt;= 0,90).
+  + Xử lý vùng đệm (Medium Confidence): Đối với các giao dịch có độ tự tin trung bình, hệ thống KHÔNG KHÓA mà áp dụng biện pháp ma sát nhẹ: yêu cầu người dùng xác thực sinh trắc học / OTP nâng cao (Step-up Authentication) hoặc đẩy vào hàng đợi kiểm tra sau của đội kiểm soát gian lận.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tác động tiêu cực của FP đối với trải nghiệm khách hàng (Customer Friction / False Alarm Fatigue). Trong kiểm soát gian lận thanh toán, khóa nhầm một khách hàng trung thành gây thiệt hại doanh thu và danh tiếng lớn hơn nhiều so với việc để một giao dịch nghi vấn đi qua luồng kiểm tra phụ (Step-up Auth).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Provost, F., &amp; Fawcett, T. Data Science for Business; FTC - Aiming for truth, fairness, and equity in your company's use of AI (https://www.ftc.gov/business-guidance/blog/2021/04/aiming-truth-fairness-equity-your-companys-use-ai).</t>
         </is>
       </c>
     </row>
@@ -1129,10 +1267,24 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định lỗi nào tạo tác động ngay và lỗi nào còn qua bước xem xét.
-Phân tích theo nguyên lý thiết kế: Xác định lỗi nào tạo tác động ngay và lỗi nào còn qua bước xem xét.</t>
+- Chọn đúng hướng ưu tiên Precision (1.0 điểm): Lập luận chọn Precision vì FP làm gián đoạn lớp học ngay, còn FN vẫn có người kiểm tra sau.
+- Chính sách phân luồng 3 cấp độ rõ ràng (1.0 điểm): Phân luồng tự động chặn (confidence cực cao), hàng đợi người duyệt và tự động thông qua.
+- Nêu đủ các chỉ số theo dõi trọng yếu (1.0 điểm): Theo dõi tỷ lệ chặn nhầm (FP rate) và thời gian giải phóng hàng đợi người duyệt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đề xuất hướng ưu tiên Precision / Recall:
+Bắt buộc phải ưu tiên TỐI ĐA HÓA PRECISION (High Precision Policy).
+Lý do: False Positive (FP) gây hậu quả ngay lập tức và phá vỡ tiến trình nghiệp vụ cốt lõi (chặn nhầm tài liệu học tập hợp lệ, làm gián đoạn buổi giảng dạy của giảng viên và học viên). Ngược lại, False Negative (FN) không gây tác hại ngay tức thì vì tài liệu chưa tự động xuất bản mà chỉ đi vào hàng đợi xem xét của chuyên viên kiểm duyệt nội dung ở tuyến sau.
+2. Chính sách phân luồng 3 cấp độ (Three-Tier Routing Policy):
+- Cấp độ 1 (Tự động chặn - High Confidence Violation): Chỉ tự động chặn ngay lập tức khi mô hình đạt độ tin cậy vi phạm cực cao (Confidence &gt;= 0,95) đối với các lỗi nghiêm trọng (nội dung bạo lực, vi phạm bản quyền trắng trợn).
+- Cấp độ 2 (Hàng đợi kiểm duyệt - Ambiguous Review): Khi độ tin cậy vi phạm nằm trong vùng nghi vấn (0,50 &lt;= Confidence &lt; 0,95), tài liệu được chuyển vào hàng đợi người kiểm duyệt duyệt trước, tạm thời chưa phát hành công khai.
+- Cấp độ 3 (Tự động duyệt - Safe Pass): Khi độ tin cậy vi phạm &lt; 0,50, tài liệu được tự động thông qua để đảm bảo tiến độ lớp học.
+3. Các chỉ số bắt buộc phải theo dõi:
+- Tỷ lệ chặn nhầm (False Positive Rate): Tỷ lệ tài liệu giáo dục hợp lệ bị mô hình chặn nhầm.
+- Thời gian trung bình giải phóng hàng đợi xem xét (Average Queue Review Time): Đảm bảo hàng đợi xem xét không trở thành nút thắt làm chậm tài liệu của giáo viên.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mô hình kiểm duyệt nội dung kết hợp (Human-in-the-loop Content Moderation): Thiết kế bất đối xứng tận dụng khâu người duyệt ở hạ lưu để bù đắp cho sai số của mô hình. Bằng cách chỉ chặn tự động ở ngưỡng Precision cực cao, hệ thống bảo vệ hoạt động giảng dạy không bị gián đoạn oan uổng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Roberts, S. T. (2019). Behind the Screen: Content Moderation in the Shadows of Social Media. Yale University Press; Google PAIR Guidebook - Human-in-the-loop (https://pair.withgoogle.com/guidebook/).</t>
         </is>
       </c>
     </row>
@@ -1164,10 +1316,28 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng để xác suất nhỏ che một hậu quả thảm họa chưa được kiểm thử.
-Phân tích theo nguyên lý thiết kế: Đừng để xác suất nhỏ che một hậu quả thảm họa chưa được kiểm thử.</t>
+- Thứ tự ưu tiên chính xác (1.0 điểm): Xếp đúng R2 (ưu tiên 1 - thảm họa chưa test), R3 (ưu tiên 2 - thiếu mẫu), R1 (ưu tiên 3 - rủi ro thấp/log rõ).
+- Ghi rõ độ không chắc chắn và người phụ trách (1.0 điểm): Gán đúng DPO/Security cho R2, SRE cho R3 và Backend cho R1 kèm đánh giá độ không chắc chắn.
+- Bước xác minh kỹ thuật tiếp theo cụ thể (1.0 điểm): Nêu rõ Adversarial test cho R2, Load test cho R3 và tối ưu hàng đợi cho R1.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thứ tự ưu tiên biện pháp xử lý rủi ro: R2 -&gt; R3 -&gt; R1.
+2. Phân tích chi tiết độ không chắc chắn, người phụ trách và bước xác minh tiếp theo:
+- Ưu tiên 1: R2 (Gửi nhầm dữ liệu cá nhân - Xác suất ước lượng 0,2%, Mức độ cực cao / Thảm họa)
+  + Độ không chắc chắn: Cực kỳ cao, vì con số 0,2% chỉ là ước lượng lý thuyết và hệ thống 'chưa từng kiểm tra sức chịu đựng' (Stress testing).
+  + Người phụ trách: Cán bộ Bảo vệ Dữ liệu (DPO) phối hợp cùng Kỹ sư Trưởng An toàn Thông tin (Security Lead).
+  + Bước xác minh tiếp theo: Thiết kế bài kiểm thử thâm nhập đối kháng (Adversarial Data Leakage Test) và kiểm tra ranh giới PII masking ngay trong sprint này.
+- Ưu tiên 2: R3 (Công cụ hết thời gian chờ - Xác suất 4%, Mức độ vừa, mẫu chỉ 15 ca)
+  + Độ không chắc chắn: Cao, do cỡ mẫu 15 trường hợp là không đủ độ tin cậy thống kê.
+  + Người phụ trách: Kỹ sư Vận hành Hạ tầng (SRE Lead).
+  + Bước xác minh tiếp theo: Chạy kiểm thử tải (Load Testing) trên 500 yêu cầu đồng thời để đo lường tỷ lệ timeout thực tế và cấu hình Circuit Breaker.
+- Ưu tiên 3: R1 (Thư điện tử gửi chậm - Xác suất 20%, Mức độ thấp, có log 3 tháng)
+  + Độ không chắc chắn: Rất thấp (dữ liệu log 3 tháng có độ tin cậy cao), mức độ rủi ro thấp.
+  + Người phụ trách: Kỹ sư Phát triển Backend (Backend Engineer).
+  + Bước xác minh tiếp theo: Tối ưu hóa hàng đợi gửi thư Celery/Redis bất đồng bộ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Quản trị rủi ro AI theo Khung ma trận tác động bất đối xứng: Rủi ro rò rỉ dữ liệu cá nhân (R2) vi phạm luật bảo vệ dữ liệu và có thể dẫn đến phạt hành chính đình chỉ kinh doanh; do đó dù xác suất ước lượng thấp, nó vẫn là ưu tiên số 1 tuyệt đối. Tuyệt đối không để xác suất nhỏ che mờ hậu quả thảm họa chưa kiểm chứng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+ISO 31000:2018 - Risk Management Guidelines (https://www.iso.org/standard/65694.html); Taleb, N. N. - Antifragile: Things That Gain from Disorder.</t>
         </is>
       </c>
     </row>
@@ -1207,10 +1377,28 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đưa các lỗi có hậu quả không đảo ngược và lỗi làm mất trạng thái lên trước; tốc độ chỉ là chỉ số phụ.
-Phân tích theo nguyên lý thiết kế: Đưa các lỗi có hậu quả không đảo ngược và lỗi làm mất trạng thái lên trước; tốc độ chỉ là chỉ số phụ.</t>
+- Thứ tự ưu tiên 5 thẻ chuẩn xác (1.0 điểm): Xếp đúng C -&gt; D -&gt; E lên trước (chặn rủi ro cao), sau đó đến B và A.
+- Giải thích 3 thẻ phải chặn và điều kiện đạt (1.0 điểm): Nêu rõ lý do chặn thẻ C (hạn mức 100tr), thẻ D (ảo giác nguồn), thẻ E (timeout) và điều kiện đạt tương ứng.
+- Chọn chỉ số so với mốc nền 11 phút (1.0 điểm): Nêu rõ chỉ số thời gian đối chiếu trung vị giảm từ 11 phút xuống dưới 3 phút.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thứ tự ưu tiên kiểm thử cho 5 thẻ (Test Cards Prioritization):
+Thứ tự ưu tiên: C -&gt; D -&gt; E -&gt; B -&gt; A.
+Giải thích: Các thẻ có rủi ro không thể đảo ngược (vượt hạn mức tài chính) và rủi ro mất trạng thái kiểm toán phải được ưu tiên kiểm tra trước; sau đó mới đến xử lý lỗi ngoại lệ biên và cuối cùng là trường hợp thuận lợi.
+2. Giải thích 3 thẻ BẮT BUỘC PHẢI CHẶN trước khi chạy Pilot và Điều kiện đạt:
+- Thẻ C (Hóa đơn trên 100 triệu, trường dữ liệu đủ):
+  + Lý do chặn: Ràng buộc cứng về tài chính. Dù AI trích xuất đủ 100% dữ liệu, hóa đơn &gt; 100 triệu tuyệt đối không được phép tự động ghi sổ mà bắt buộc phải có người phê duyệt.
+  + Điều kiện đạt: Hệ thống khóa trạng thái hóa đơn và tự động điều hướng sang hàng đợi phê duyệt của Kế toán trưởng; không thể ghi sổ nếu thiếu chữ ký số.
+- Thẻ D (Trích dẫn chỉ ra sai dòng nguồn):
+  + Lý do chặn: Rủi ro ảo giác trích dẫn (Hallucination). Trích dẫn sai nguồn làm mất tính kiểm toán và có thể dẫn đến đối soát sai lệch số tiền.
+  + Điều kiện đạt: Bộ kiểm tra trích dẫn phát hiện dòng nguồn không khớp với văn bản gốc, tự động gắn cờ cảnh báo 'Sai lệch trích dẫn' và yêu cầu kế toán đối chiếu lại.
+- Thẻ E (Dịch vụ kiểm tra hết thời gian chờ - Timeout):
+  + Lý do chặn: Lỗi hệ thống. Nếu timeout mà hệ thống âm thầm bỏ qua kiểm tra và tự ghi sổ thì sẽ lọt hóa đơn rác.
+  + Điều kiện đạt: Giao dịch bị tạm ngưng an toàn, đưa vào hàng đợi chờ thử lại và thông báo cho người dùng trạng thái đang xử lý.
+3. Chỉ số đo lường chính so với mốc nền 11 phút: Thời gian chu trình đối chiếu trung vị của kế toán (Median Invoice Reconciliation Time) với mục tiêu giảm từ 11 phút xuống dưới 3 phút/hóa đơn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Ưu tiên Kiểm thử theo Mức độ Rủi ro Tài chính (Risk-Weighted Test Prioritization): Thẻ C (&gt; 100 triệu) và Thẻ D (ảo giác trích dẫn) là hai rủi ro trực tiếp gây thất thoát tài sản và vi phạm pháp lý kế toán. Không bao giờ được phép pilot khi hai rào chắn này chưa được chứng minh hoạt động hoàn hảo.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Testing for Reliability (https://sre.google/sre-book/testing-for-reliability/); Sarbanes-Oxley Act (SOX) Section 404 - Internal Controls over Financial Reporting.</t>
         </is>
       </c>
     </row>
@@ -1243,10 +1431,24 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định thứ duy nhất nhóm thử nghiệm được phép thay đổi và ai có thể ảnh hưởng lẫn nhau.
-Phân tích theo nguyên lý thiết kế: Xác định thứ duy nhất nhóm thử nghiệm được phép thay đổi và ai có thể ảnh hưởng lẫn nhau.</t>
+- Định nghĩa rõ nhóm đối chứng và thử nghiệm (1.0 điểm): Nhóm A dùng onboarding tĩnh, nhóm B có gợi ý bước tiếp theo theo ngữ cảnh động.
+- Phương pháp phân nhóm theo cụm công ty chống lây nhiễm (1.0 điểm): Lập luận sắc bén việc phân nhóm theo Company/Account level để ngăn chặn lây nhiễm giữa nhân viên cùng cty.
+- Kết quả đo chính và kiểm soát yếu tố gây nhiễu (1.0 điểm): Đo tỷ lệ hoàn thành onboarding trong 7 ngày, cố định email nhắc và phân tầng theo quy mô công ty.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế thử nghiệm A/B kiểm soát hiện tượng lây nhiễm giữa các nhóm (Cluster-Randomized A/B Test):
+1. Nhóm đối chứng và Nhóm thử nghiệm:
+- Nhóm đối chứng (Control A): Trải nghiệm quy trình bắt đầu sử dụng (Onboarding) thông thường với danh sách công việc tĩnh cố định.
+- Nhóm thử nghiệm (Treatment B): Trải nghiệm quy trình Onboarding có 'Gợi ý bước tiếp theo theo ngữ cảnh động' (Dynamic Contextual Next-Step Suggestions) được cá nhân hóa dựa trên hành vi vừa thực hiện của người dùng.
+2. Phương pháp phân nhóm chống lây nhiễm (Cluster Randomization):
+- Ràng buộc: Người dùng trong cùng một công ty thường xuyên giao tiếp, hướng dẫn nhau và làm việc chung. Nếu phân nhóm theo User ID cá nhân, người dùng nhóm B sẽ chỉ cho người dùng nhóm A hoặc ngược lại, gây hiện tượng lây nhiễm dữ liệu (Network Spillover / Contamination Bias).
+- Giải pháp phân nhóm: Bắt buộc phải PHÂN NHÓM THEO CỤM CÔNG TY / TỔ CHỨC (Cluster Randomization at the Company/Account Level). 100% nhân viên thuộc Công ty X sẽ vào nhóm A, và 100% nhân viên thuộc Công ty Y sẽ vào nhóm B.
+3. Kết quả đo lường và Kiểm soát biến gây nhiễu:
+- Kết quả đo chính: Tỷ lệ người dùng mới hoàn tất toàn bộ quy trình onboarding trong vòng 7 ngày đầu tiên (7-day Onboarding Completion Rate).
+- Kiểm soát biến gây nhiễu: Tuyệt đối giữ nguyên không thay đổi nội dung email nhắc nhở, không thay đổi nội dung các bài học, và phân tầng ngẫu nhiên (Stratified Sampling) theo quy mô công ty (công ty nhỏ vs doanh nghiệp lớn) để hai nhóm cân bằng về độ phức tạp nghiệp vụ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Thử nghiệm phân cụm (Cluster-Randomized Controlled Trial) trong sản phẩm B2B: Khi các đối tượng thử nghiệm có tương tác xã hội hoặc chung quy trình tổ chức, phân nhóm theo cá thể sẽ làm sai lệch hoàn toàn kết quả A/B test. Phân nhóm theo Account/Company là chuẩn mực vàng để loại bỏ hiệu ứng lây lan mạng lưới (Spillover Effects).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kohavi, R., et al. (2020). Trustworthy Online Controlled Experiments (Cluster Randomization) (https://exp-platform.com/); Gui, H., et al. (2015). Network A/B Testing: From Sampling to Estimation. WWW 2015.</t>
         </is>
       </c>
     </row>
@@ -1282,10 +1484,29 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nhìn vào thứ tự xảy ra và nguồn gây lỗi; đừng chỉ đếm xem có bao nhiêu thành phần trong sơ đồ.
-Phân tích theo nguyên lý thiết kế: Nhìn vào thứ tự xảy ra và nguồn gây lỗi; đừng chỉ đếm xem có bao nhiêu thành phần trong sơ đồ.</t>
+- Phân loại chuẩn xác bản chất 5 loại lỗi (1.5 điểm): Xác định đúng timeout bên ngoài (A), lỗi hợp đồng thiếu trường (B), tấn công gián tiếp đối kháng (C), lỗi hạ tầng (D) và lỗi tuần tự TOCTOU (E).
+- Tín hiệu đạt quan sát được rõ ràng cho từng thẻ (1.5 điểm): Nêu đủ tín hiệu chặn không cho đi tiếp, bắt lỗi schema, từ chối gọi tool, mở circuit breaker và bắt lệch mã hash SHA-256.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân loại 5 thẻ kiểm thử và tín hiệu đạt quan sát được:
+1. Thẻ A (Bộ quét mã độc hết thời gian chờ - Timeout):
+- Phân loại: Lỗi phụ thuộc bên ngoài / Lỗi đơn (External Dependency / Component Timeout Failure).
+- Tín hiệu đạt quan sát được: Tài liệu bị tạm ngưng xử lý an toàn; hệ thống ghi log cảnh báo mã lỗi `SCANNER_TIMEOUT` và tự động kích hoạt thử lại tối đa 2 lần; tuyệt đối không cho phép tài liệu đi tiếp vào bộ phân tích khi chưa có kết quả quét sạch.
+2. Thẻ B (Bộ quét trả đạt nhưng bộ phân tích trả thiếu trường):
+- Phân loại: Lỗi kết hợp / Lỗi hợp đồng giao diện dữ liệu (Interface Contract / Partial Data Failure).
+- Tín hiệu đạt quan sát được: Bộ xác thực schema phát hiện thiếu các trường bắt buộc; đánh dấu tài liệu là 'Dữ liệu khiếm khuyết', ngăn chặn việc đưa vào chỉ mục truy hồi và gửi thông báo cho người dùng yêu cầu kiểm tra lại định dạng tệp.
+3. Thẻ C (Tài liệu chứa chỉ dẫn độc hại yêu cầu mô hình gọi công cụ):
+- Phân loại: Lỗi đối kháng / Tấn công chèn mã gián tiếp (Adversarial Indirect Prompt Injection Attack).
+- Tín hiệu đạt quan sát được: Bộ lọc Guardrail nội dung phát hiện chỉ dẫn độc hại hoặc mô hình từ chối thực thi lệnh gọi công cụ trái phép; hệ thống chỉ trích xuất dữ liệu thụ động mà không kích hoạt bất kỳ action nào ra bên ngoài.
+4. Thẻ D (Dịch vụ chỉ mục truy hồi không truy cập được):
+- Phân loại: Lỗi hạ tầng hệ thống bên ngoài (Infrastructure Availability Failure).
+- Tín hiệu đạt quan sát được: Circuit Breaker mở, chuyển giao diện sang chế độ tra cứu dự phòng tĩnh và hiển thị cảnh báo dịch vụ đang bảo trì.
+5. Thẻ E (Tài liệu bị thay đổi sau khi quét nhưng trước khi lập chỉ mục):
+- Phân loại: Lỗi tuần tự / Lỗ hổng tính toàn vẹn thời gian kiểm tra đến thời gian sử dụng (TOCTOU - Time-of-Check to Time-of-Use Attack).
+- Tín hiệu đạt quan sát được: Hệ thống kiểm tra mã băm toàn vẹn (SHA-256 Hash Mismatch), lập tức từ chối lập chỉ mục và kích hoạt cảnh báo an ninh.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Mô hình kiểm thử hỏng hóc bảo mật và độ tin cậy trong đường ống RAG. Đặc biệt, Thẻ C (Indirect Prompt Injection) và Thẻ E (TOCTOU Integrity Violation) là các lỗ hổng kinh điển trong hệ thống AI. Kiểm soát tính toàn vẹn bằng SHA-256 hash và cô lập dữ liệu untrusted là tiêu chuẩn bắt buộc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLMs - LLM01: Prompt Injection &amp; LLM05: Supply Chain Vulnerabilities (https://owasp.org/www-project-top-10-for-large-language-model-applications/); CWE-367: Time-of-check Time-of-use (TOCTOU) Race Condition.</t>
         </is>
       </c>
     </row>
@@ -1322,10 +1543,22 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách phần đã có bằng chứng khỏi 3% chưa được kiểm chứng.
-Phân tích theo nguyên lý thiết kế: Tách phần đã có bằng chứng khỏi 3% chưa được kiểm chứng.</t>
+- Ra quyết định Scoped Go / Conditional Go chính xác (1.0 điểm): Lựa chọn Go có điều kiện cho pilot, giữ nguyên vai trò con người quyết định.
+- Khoanh vùng phạm vi an toàn loại trừ 3% (1.0 điểm): Nêu rõ việc triển khai cho 97% ngôn ngữ chính và chuyển 3% ngôn ngữ hiếm cho con người xử lý.
+- Khoảng trống cần đóng và điều kiện dừng rõ ràng (1.0 điểm): Thu thập dữ liệu ngôn ngữ hiếm và đặt điều kiện dừng rollback khi tỷ lệ override &gt; 30%.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định chính thức cho đợt thử nghiệm này: QUYẾT ĐỊNH CHO PHÉP THỬ NGHIỆM CÓ ĐIỀU KIỆN (CONDITIONAL GO / SCOPED PILOT GO).
+2. Phạm vi triển khai hẹp an toàn (Scoped Pilot Boundary):
+- Giới hạn phạm vi: Chỉ triển khai thử nghiệm trên 97% lưu lượng thuộc các ngôn ngữ chính đã được kiểm chứng đầy đủ và có bằng chứng vượt trội so với mốc nền.
+- Cơ chế loại trừ chủ động: Hệ thống tự động nhận diện và loại trừ 100% các phiếu hỗ trợ bằng ngôn ngữ hiếm (3% lưu lượng chưa kiểm thử) ngay tại tầng tiếp nhận và chuyển tiếp trực tiếp sang cho nhân viên chuyên trách xử lý thủ công (Zero-AI fallback).
+- Giữ vững vai trò con người: Nhân viên hỗ trợ luôn là người đưa ra quyết định cuối cùng về nhãn ưu tiên, AI chỉ đóng vai trò gợi ý (Augmentation Mode).
+3. Khoảng trống kỹ thuật phải đóng trong quá trình Pilot và Điều kiện dừng khẩn cấp:
+- Khoảng trống phải đóng: Song song với quá trình chạy pilot, đội ngũ phải thu thập mẫu dữ liệu thực tế của 3% ngôn ngữ hiếm để xây dựng bộ đánh giá bổ sung.
+- Điều kiện dừng khẩn cấp (Pilot Abort Trigger): Nếu tỷ lệ nhân viên từ chối hoặc sửa lại gợi ý của AI (Override Rate) vượt quá 30% trong 2 tuần liên tiếp, HOẶC phát sinh lỗi phân loại sai gây vi phạm SLA nghiêm trọng, hệ thống tự động kích hoạt tính năng Rollback để quay về quy trình thủ công 100%.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Chiến lược ra quyết định 'Scoped Go' (Triển khai có ranh giới): Khi 97% hệ thống đã sẵn sàng và có giá trị kinh doanh vượt mốc nền, việc đình chỉ toàn bộ dự án vì 3% trường hợp biên là cứng nhắc không cần thiết. Bằng cách khoanh vùng và cách ly 3% ngoại lệ sang luồng con người, tổ chức vừa tạo ra giá trị tức thì vừa kiểm soát tuyệt đối rủi ro.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cagan, M. (2017). Inspired (Pilot Strategies); Google PAIR Guidebook - Phased Rollout (https://pair.withgoogle.com/guidebook/).</t>
         </is>
       </c>
     </row>
@@ -1360,10 +1593,33 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra theo đối chứng, đánh giá, kiểm soát và vận hành.
-Phân tích theo nguyên lý thiết kế: Kiểm tra theo đối chứng, đánh giá, kiểm soát và vận hành.</t>
+- Lập sổ khoảng trống đủ 4 trụ cột (1.5 điểm): Nêu rõ bằng chứng cần tạo và người phụ trách cho Đối chứng (PM), An toàn đối kháng (QA/Security), Kiểm soát hành động (Tech Lead) và Vận hành on-call (SRE).
+- Ra quyết định hoãn phát hành chuẩn xác (1.5 điểm): Khẳng định Not-Yet/Tạm hoãn phát hành, giải thích rõ demo 18/20 chọn trước không phản ánh năng lực production.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Sổ rà soát khoảng trống từ Demo đến Production (Demo-to-Production Gap Register):
+1. Sổ khoảng trống chi tiết theo 4 trụ cột kỹ thuật:
+- Trụ cột 1 (Đo lường &amp; Đối chứng - Benchmarking):
+  + Khoảng trống: Chưa so sánh hiệu quả với hệ thống tìm kiếm hiện tại; kết quả 18/20 câu chỉ là dữ liệu chọn trước (cherry-picked demo).
+  + Bằng chứng cần tạo: Báo cáo thử nghiệm đối chứng mù đôi (A/B Benchmark) trên 200 truy vấn thực tế ngẫu nhiên so sánh với hệ thống cũ.
+  + Người phụ trách: Quản lý Sản phẩm (Product Manager).
+- Trụ cột 2 (Chất lượng &amp; An toàn - Robustness &amp; Safety):
+  + Khoảng trống: Chưa kiểm thử trên lưu lượng đại diện hoặc các trường hợp đối kháng (Prompt Injection, OOD queries).
+  + Bằng chứng cần tạo: Bộ kiểm thử Red-teaming gồm 50 ca tấn công đối kháng và 100 ca biên lỗi nguồn.
+  + Người phụ trách: Kỹ sư Đảm bảo Chất lượng AI / Security Engineer.
+- Trụ cột 3 (Kiểm soát tác động - Governance &amp; Safe Actions):
+  + Khoảng trống: Tác động qua công cụ chưa có cơ chế phê duyệt hoặc rollback khi gọi API bên ngoài.
+  + Bằng chứng cần tạo: Tích hợp cổng Human-in-the-loop xác nhận trước khi thực thi action và cơ chế hoàn tác giao dịch.
+  + Người phụ trách: Kỹ sư Backend / Tech Lead.
+- Trụ cột 4 (Vận hành &amp; Giám sát - Observability &amp; On-call):
+  + Khoảng trống: Chưa có cảnh báo, nhịp cập nhật tri thức hoặc người phụ trách vận hành khi có sự cố.
+  + Bằng chứng cần tạo: Dashboard giám sát thời gian thực, lịch trực on-call và quy trình cập nhật tài liệu tự động.
+  + Người phụ trách: Kỹ sư Vận hành SRE Lead.
+2. Quyết định phát hành chính thức:
+QUYẾT ĐỊNH: TẠM HOÃN PHÁT HÀNH (NOT-YET / NO-GO CHO PRODUCTION). Tuyệt đối không đưa vào sản xuất cho đến khi 100% bằng chứng của 4 trụ cột trên được nghiệm thu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: 'Vực sâu tử thần giữa Demo và Production' (The Demo-to-Production Chasm). Một bản demo 18/20 câu chọn trước chỉ có giá trị truyền thông nội bộ. Chỉ khi hệ thống vượt qua kiểm thử đối chứng, kiểm thử đối kháng, có cổng kiểm soát hành động và trực vận hành 24/7 thì mới đủ tư cách phát hành ra môi trường sản xuất thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Sculley, D., et al. (2015). Hidden Technical Debt in Machine Learning Systems. NeurIPS 2015 (https://papers.nips.cc/paper/5656-hidden-technical-debt-in-machine-learning-systems.pdf); Google SRE Book - Launching Software (https://sre.google/sre-book/release-engineering/)</t>
         </is>
       </c>
     </row>
